--- a/reports/hours_12-2025.xlsx
+++ b/reports/hours_12-2025.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>אגירה</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>גב ים</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>שיחת זום עם אלקטרה</t>
+          <t>פגישה במועצה</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="G122" t="inlineStr"/>
     </row>
@@ -4212,17 +4212,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>אגירה</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>השגה משפטית</t>
+          <t>גב ים</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>התכתבות מרחב ירושלים לענין השגה משפטית</t>
+          <t>שיחת זום עם אלקטרה</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G123" t="inlineStr"/>
     </row>
@@ -4243,17 +4243,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>קניון דרורים</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>היתר בניה</t>
+          <t>השגה משפטית</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>מכתב לרמ"י</t>
+          <t>התכתבות מרחב ירושלים לענין השגה משפטית</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G124" t="inlineStr"/>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ינושבסקי</t>
+          <t>קניון דרורים</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>אבן גבירול</t>
+          <t>היתר בניה</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>תוספת להסכם מרפסות</t>
+          <t>מכתב לרמ"י</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G125" t="inlineStr"/>
     </row>
@@ -4305,17 +4305,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>ינושבסקי</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>מגידו</t>
+          <t>אבן גבירול</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>עץ החזקות לרמ"י</t>
+          <t>תוספת להסכם מרפסות</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4331,22 +4331,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>24.12.2025</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>אלון קפלן</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>חרוזים</t>
+          <t>מגידו</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>שיחת זום רון</t>
+          <t>עץ החזקות לרמ"י</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4367,17 +4367,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ש.ב.ה</t>
+          <t>אלון קפלן</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>פרויקט נקסט</t>
+          <t>חרוזים</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>שיחת זום לעניין הסכמי מכירה</t>
+          <t>שיחת זום רון</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>הגירה</t>
+          <t>ש.ב.ה</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>גב ים</t>
+          <t>פרויקט נקסט</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>שיחה אלקטרה בעניין הסכם ושיחה פנימית</t>
+          <t>שיחת זום לעניין הסכמי מכירה</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" t="inlineStr"/>
     </row>
@@ -4429,17 +4429,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>הגירה</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>גב ים</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>התכתבות מאיר ושיחות יעל</t>
+          <t>שיחה אלקטרה בעניין הסכם ושיחה פנימית</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr"/>
     </row>
@@ -4460,17 +4460,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>הטלים</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>בדיקה לעניין הטלי סלילה לעומת היתר בנייה</t>
+          <t>התכתבות מאיר ושיחות יעל</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>גבעוני</t>
+          <t>קניון דרורים</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>השגה שמאית</t>
+          <t>היתר בניה</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>שיחה בני שמאי וטופס השגה</t>
+          <t>רמי לעניין בקשה להיתר</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="G132" t="inlineStr"/>
     </row>
@@ -4522,17 +4522,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ינושבסקי</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>אבן גבירול</t>
+          <t>הטלים</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>שיחות בעניין חנייה רוזן</t>
+          <t>בדיקה לעניין הטלי סלילה לעומת היתר בנייה</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G133" t="inlineStr"/>
     </row>
@@ -4553,17 +4553,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>עקיבא איגר</t>
+          <t>גבעוני</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>השגה שמאית</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>הכנה למסירות</t>
+          <t>שיחה בני שמאי וטופס השגה</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="G134" t="inlineStr"/>
     </row>
@@ -4584,17 +4584,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>ינושבסקי</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>משאבי שדה</t>
+          <t>אבן גבירול</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>טיפול בביטול עסקה</t>
+          <t>שיחות בעניין חנייה רוזן</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="G135" t="inlineStr"/>
     </row>
@@ -4615,17 +4615,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>עקיבא איגר</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>גבעת שמואל</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>תיקון טיוטת הסכם שותפות</t>
+          <t>הכנה למסירות</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="G136" t="inlineStr"/>
     </row>
@@ -4651,12 +4651,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>גולני צפון</t>
+          <t>משאבי שדה</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>טיפול באישור עירייה</t>
+          <t>טיפול בביטול עסקה</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4672,22 +4672,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>25.12.2025</t>
+          <t>24.12.2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>עמל 10</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>פינוי בינוי</t>
+          <t>גבעת שמואל</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>שיחת זום</t>
+          <t>תיקון טיוטת הסכם שותפות</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4696,29 +4696,29 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>25.12.2025</t>
+          <t>24.12.2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>גולני צפון</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>התכתבות אורית ובדיקות שוטפות</t>
+          <t>טיפול באישור עירייה</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="G139" t="inlineStr"/>
     </row>
@@ -4739,17 +4739,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>הגירה</t>
+          <t>עמל 10</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>גב ים</t>
+          <t>פינוי בינוי</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>בדיקת גושים חלקות</t>
+          <t>שיחת זום</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="G140" t="inlineStr"/>
     </row>
@@ -4770,17 +4770,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>איילון</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>אשקלון</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>רישום זכויות</t>
+          <t>התכתבות אורית ובדיקות שוטפות</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G141" t="inlineStr"/>
     </row>
@@ -4801,17 +4801,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>סיגת</t>
+          <t>הגירה</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>הארכת חוזה</t>
+          <t>גב ים</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>שיחת מודד</t>
+          <t>בדיקת גושים חלקות</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G142" t="inlineStr"/>
     </row>
@@ -4832,17 +4832,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>קן דרור</t>
+          <t>איילון</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>מכירה חוף התכלת</t>
+          <t>אשקלון</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>שוטף</t>
+          <t>רישום זכויות</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G143" t="inlineStr"/>
     </row>
@@ -4863,17 +4863,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>סיגת</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>מבוא ביתר</t>
+          <t>הארכת חוזה</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>מכתב לרמי</t>
+          <t>שיחת מודד</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4894,17 +4894,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>קן דרור</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>פי גלילות</t>
+          <t>מכירה חוף התכלת</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>טיפול בקבלת החזר</t>
+          <t>שוטף</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>תביעה רמי</t>
+          <t>מבוא ביתר</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>שיחה יעל</t>
+          <t>מכתב לרמי</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G146" t="inlineStr"/>
     </row>
@@ -4956,17 +4956,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>אשקלון</t>
+          <t>פי גלילות</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>הסכם שכירות</t>
+          <t>טיפול בקבלת החזר</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G147" t="inlineStr"/>
     </row>
@@ -4987,17 +4987,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>אלון קפלן</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>חרוזים</t>
+          <t>תביעה רמי</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>מכר דירה 13</t>
+          <t>שיחה יעל</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G148" t="inlineStr"/>
     </row>
@@ -5018,17 +5018,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>אלון קפלן</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>אנה פרנק</t>
+          <t>אשקלון</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>טיפול באישורי מיסים</t>
+          <t>הסכם שכירות</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G149" t="inlineStr"/>
     </row>
@@ -5049,17 +5049,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>אלון קפלן</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>o.p.c.</t>
+          <t>חרוזים</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>הסכם אופציה</t>
+          <t>מכר דירה 13</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G150" t="inlineStr"/>
     </row>
@@ -5080,17 +5080,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>יואל רונן</t>
+          <t>אלון קפלן</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ריינס</t>
+          <t>אנה פרנק</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>דירה 13</t>
+          <t>טיפול באישורי מיסים</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5099,29 +5099,29 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>27.12.2025</t>
+          <t>25.12.2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>יואל רונן</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ריינס</t>
+          <t>o.p.c.</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>הסכם מאסטר</t>
+          <t>הסכם אופציה</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5130,29 +5130,29 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>27.12.2025</t>
+          <t>25.12.2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>יואל רונן</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>תביעה רמי</t>
+          <t>ריינס</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>חוות דעת מומחה רמי</t>
+          <t>דירה 13</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5161,29 +5161,29 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>28.12.2025</t>
+          <t>27.12.2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>הגירה</t>
+          <t>יואל רונן</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>ריינס</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>הסכם שותפות פגישת זום</t>
+          <t>הסכם מאסטר</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5192,29 +5192,29 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>28.12.2025</t>
+          <t>27.12.2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>אודי שגב</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>תביעה רמי</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>פגישה במשרד</t>
+          <t>חוות דעת מומחה רמי</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G155" t="inlineStr"/>
     </row>
@@ -5235,17 +5235,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>גוהר</t>
+          <t>הגירה</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>אנילביץ</t>
+          <t>עין כרמל</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>תיקון תצהיר עדות</t>
+          <t>הסכם שותפות פגישת זום</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G156" t="inlineStr"/>
     </row>
@@ -5266,17 +5266,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>אודי שגב</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>אשקלון</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>טיוטת הסכם שכירות</t>
+          <t>פגישה במשרד</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G157" t="inlineStr"/>
     </row>
@@ -5297,17 +5297,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>בוחבוט</t>
+          <t>גוהר</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>מעלות</t>
+          <t>אנילביץ</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>בקשה לבית משפט</t>
+          <t>תיקון תצהיר עדות</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G158" t="inlineStr"/>
     </row>
@@ -5328,17 +5328,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>סיגת</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>הארכת חוזה</t>
+          <t>אשקלון</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>טיפול במדידה</t>
+          <t>טיוטת הסכם שכירות</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="G159" t="inlineStr"/>
     </row>
@@ -5359,17 +5359,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>בוחבוט</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>מכירת מטמנה</t>
+          <t>מעלות</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>טיפול בקלוזינג</t>
+          <t>בקשה לבית משפט</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G160" t="inlineStr"/>
     </row>
@@ -5390,17 +5390,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>סיגת</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>אפיקים</t>
+          <t>הארכת חוזה</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>טיפול בהעברת זכויות</t>
+          <t>טיפול במדידה</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G161" t="inlineStr"/>
     </row>
@@ -5421,17 +5421,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>רונן כהן</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>מוצא</t>
+          <t>מכירת מטמנה</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>טיפול במשכנתא</t>
+          <t>טיפול בקלוזינג</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G162" t="inlineStr"/>
     </row>
@@ -5452,17 +5452,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>גבעת שמואל</t>
+          <t>אפיקים</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>נספח חניות</t>
+          <t>טיפול בהעברת זכויות</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5483,17 +5483,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>קן דרור</t>
+          <t>רונן כהן</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>בצרה</t>
+          <t>מוצא</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>טיפול ברישום זכויות</t>
+          <t>טיפול במשכנתא</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G164" t="inlineStr"/>
     </row>
@@ -5514,17 +5514,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ש.ב.ה</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>שכירות ארגניה</t>
+          <t>גבעת שמואל</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>טיוטת הסכם</t>
+          <t>נספח חניות</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G165" t="inlineStr"/>
     </row>
@@ -5545,17 +5545,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>נייר חדרה</t>
+          <t>קן דרור</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>o.p.c</t>
+          <t>בצרה</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>תיקון טיוטת הסכם מכר</t>
+          <t>טיפול ברישום זכויות</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5564,29 +5564,29 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>29.12.2025</t>
+          <t>28.12.2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>קן דרור</t>
+          <t>ש.ב.ה</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>מכירה חוף התכלת</t>
+          <t>שכירות ארגניה</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>חתימת חוזה בועז</t>
+          <t>טיוטת הסכם</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5595,29 +5595,29 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>29.12.2025</t>
+          <t>28.12.2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>גוהר</t>
+          <t>נייר חדרה</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>אנילביץ</t>
+          <t>o.p.c</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>שיחת זום לעניין תצהירים</t>
+          <t>תיקון טיוטת הסכם מכר</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>קן דרור</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>השגה משפטית</t>
+          <t>מכירה חוף התכלת</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>בקשה לקבלת החלטה לרמי</t>
+          <t>חתימת חוזה בועז</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5669,17 +5669,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>גוהר</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>היטלים</t>
+          <t>אנילביץ</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>בקשה לבית משפט להוספת נספח</t>
+          <t>שיחת זום לעניין תצהירים</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G170" t="inlineStr"/>
     </row>
@@ -5700,17 +5700,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>בלצינסקי</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>שכירות נתניה</t>
+          <t>השגה משפטית</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>בדיקת חובות</t>
+          <t>בקשה לקבלת החלטה לרמי</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ש.ב.ה</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>מכירת מניות</t>
+          <t>היטלים</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>טיוטת הסכם</t>
+          <t>בקשה לבית משפט להוספת נספח</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G172" t="inlineStr"/>
     </row>
@@ -5762,17 +5762,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>הגירה</t>
+          <t>בלצינסקי</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>גב ים</t>
+          <t>שכירות נתניה</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>תיקון טיוטה</t>
+          <t>בדיקת חובות</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5793,17 +5793,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>ש.ב.ה</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>פרלל</t>
+          <t>מכירת מניות</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>תיקונים לתוספת להסכם</t>
+          <t>טיוטת הסכם</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G174" t="inlineStr"/>
     </row>
@@ -5824,17 +5824,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>הגירה</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>תחנת סורק</t>
+          <t>גב ים</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>דיון שמאים  לעניין החלטת רמי בהגשת השגה והתכתבות ועדת השגות</t>
+          <t>תיקון טיוטה</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="G175" t="inlineStr"/>
     </row>
@@ -5855,17 +5855,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>מכירת מטמנה</t>
+          <t>פרלל</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>הערכות לקלוזינג</t>
+          <t>תיקונים לתוספת להסכם</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G176" t="inlineStr"/>
     </row>
@@ -5886,17 +5886,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ינושבסקי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>אבן גבירול</t>
+          <t>תחנת סורק</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>טיפול בחנייה רוזן</t>
+          <t>דיון שמאים  לעניין החלטת רמי בהגשת השגה והתכתבות ועדת השגות</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G177" t="inlineStr"/>
     </row>
@@ -5917,17 +5917,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>יאיר לוי</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>מכירת מטמנה</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>הכנה לדיון</t>
+          <t>הערכות לקלוזינג</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G178" t="inlineStr"/>
     </row>
@@ -5948,17 +5948,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>מנורה</t>
+          <t>ינושבסקי</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>שדרות המגנים</t>
+          <t>אבן גבירול</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>בדיקת זכויות</t>
+          <t>טיפול בחנייה רוזן</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5967,29 +5967,29 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>30.12.2025</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>תחנת סורק</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>דיון שמאי מחוזי והכנה</t>
+          <t>הכנה לדיון</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5998,29 +5998,29 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>30.12.2025</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>מנורה</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>פרלל</t>
+          <t>שדרות המגנים</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>שיחת ועידה פנימית</t>
+          <t>בדיקת זכויות</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G181" t="inlineStr"/>
     </row>
@@ -6041,17 +6041,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ש.ב.א</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>תביעה רמי</t>
+          <t>תחנת סורק</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>שיחה מודד אברבוך</t>
+          <t>דיון שמאי מחוזי והכנה</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="G182" t="inlineStr"/>
     </row>
@@ -6072,17 +6072,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>אושירה</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>פרלל</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>שיחת הכנה לדיון</t>
+          <t>שיחת ועידה פנימית</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G183" t="inlineStr"/>
     </row>
@@ -6103,17 +6103,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>משרד</t>
+          <t>ש.ב.א</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>תביעה רמי</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>פגישה אביעד לעניין שכר טרחה</t>
+          <t>שיחה מודד אברבוך</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="G184" t="inlineStr"/>
     </row>
@@ -6134,17 +6134,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>אילנית חסן</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>מכירת דירה</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>נספח להסכם</t>
+          <t>שיחת הכנה לדיון</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G185" t="inlineStr"/>
     </row>
@@ -6165,17 +6165,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ינושבסקי</t>
+          <t>משרד</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>אבן גבירול</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>תוספת להסכם</t>
+          <t>פגישה אביעד לעניין שכר טרחה</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="G186" t="inlineStr"/>
     </row>
@@ -6196,17 +6196,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>רוך ברגר</t>
+          <t>אילנית חסן</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>רישום זכויות</t>
+          <t>מכירת דירה</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>השלמת מסמכים</t>
+          <t>נספח להסכם</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G187" t="inlineStr"/>
     </row>
@@ -6227,17 +6227,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>כפיר דהן</t>
+          <t>ינושבסקי</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>אבן גבירול</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>טיפול במיסוי מקרקעין</t>
+          <t>תוספת להסכם</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6246,29 +6246,29 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>31.12.2025</t>
+          <t>30.12.2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>מפעלי נשק</t>
+          <t>רוך ברגר</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>השגה משפטית</t>
+          <t>רישום זכויות</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>טיפול בהשגה משפטית ביקור ברמי ירושלים</t>
+          <t>השלמת מסמכים</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6277,29 +6277,29 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>31.12.2025</t>
+          <t>30.12.2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>דלק</t>
+          <t>כפיר דהן</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>מבוא ביתר</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>היתר בנייה ביקור ברמי ירושלים</t>
+          <t>טיפול במיסוי מקרקעין</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G190" t="inlineStr"/>
     </row>
@@ -6320,17 +6320,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>אגרוטופ</t>
+          <t>מפעלי נשק</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>תימורים</t>
+          <t>השגה משפטית</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ביקור ברמי ירושלים</t>
+          <t>טיפול בהשגה משפטית ביקור ברמי ירושלים</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>פי גלילות</t>
+          <t>מבוא ביתר</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>טיפול בהחזר תשלום ביקור ברמי</t>
+          <t>היתר בנייה ביקור ברמי ירושלים</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6382,17 +6382,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>יעל רוטשילד</t>
+          <t>אגרוטופ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>מבשרת ציון</t>
+          <t>תימורים</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>דיון בהתנגדות ושיחות הכנה</t>
+          <t>ביקור ברמי ירושלים</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>יאיר לוי</t>
+          <t>דלק</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>מכירת מטמנה</t>
+          <t>פי גלילות</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>טיפול בקלוזינג</t>
+          <t>טיפול בהחזר תשלום ביקור ברמי</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6444,17 +6444,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>אושירה</t>
+          <t>יעל רוטשילד</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>פרלל</t>
+          <t>מבשרת ציון</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>תיקון תוספת להסכם והפצה</t>
+          <t>דיון בהתנגדות ושיחות הכנה</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G195" t="inlineStr"/>
     </row>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>טיפול במיסוי</t>
+          <t>טיפול בקלוזינג</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="G196" t="inlineStr"/>
     </row>
@@ -6506,28 +6506,90 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
+          <t>אושירה</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>פרלל</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>תיקון תוספת להסכם והפצה</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>31.12.2025</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>יאיר לוי</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>מכירת מטמנה</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>טיפול במיסוי</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>31.12.2025</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
           <t>קן דרור</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>מכירה חוף התכלת</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>נספחים להסכם</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>גלית</t>
-        </is>
-      </c>
-      <c r="F197" t="n">
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
         <v>0.75</v>
       </c>
-      <c r="G197" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
